--- a/data/screener/SBIN.xlsx
+++ b/data/screener/SBIN.xlsx
@@ -4054,7 +4054,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>1061.45</v>
+        <v>1055.95</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -4062,7 +4062,7 @@
         <v>79</v>
       </c>
       <c r="B9">
-        <v>979878.78</v>
+        <v>974707.14</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -4075,34 +4075,34 @@
         <v>38</v>
       </c>
       <c r="B16" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C16" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D16" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E16" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F16" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G16" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H16" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I16" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J16" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K16" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4110,34 +4110,34 @@
         <v>6</v>
       </c>
       <c r="B17">
-        <v>220632.75</v>
+        <v>230447.1</v>
       </c>
       <c r="C17">
-        <v>230447.1</v>
+        <v>228970.28</v>
       </c>
       <c r="D17">
-        <v>228970.28</v>
+        <v>253322.17</v>
       </c>
       <c r="E17">
-        <v>253322.17</v>
+        <v>269851.66</v>
       </c>
       <c r="F17">
-        <v>269851.66</v>
+        <v>278115.48</v>
       </c>
       <c r="G17">
-        <v>278115.48</v>
+        <v>289972.69</v>
       </c>
       <c r="H17">
-        <v>289972.69</v>
+        <v>350844.58</v>
       </c>
       <c r="I17">
-        <v>350844.58</v>
+        <v>439188.51</v>
       </c>
       <c r="J17">
-        <v>439188.51</v>
+        <v>490312.7</v>
       </c>
       <c r="K17">
-        <v>490937.79</v>
+        <v>514932.59</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4160,34 +4160,34 @@
         <v>83</v>
       </c>
       <c r="B21">
-        <v>797.06</v>
+        <v>870.96</v>
       </c>
       <c r="C21">
-        <v>870.96</v>
+        <v>971.9</v>
       </c>
       <c r="D21">
-        <v>971.9</v>
+        <v>1057.77</v>
       </c>
       <c r="E21">
-        <v>1057.77</v>
+        <v>1121.27</v>
       </c>
       <c r="F21">
-        <v>1121.27</v>
+        <v>1116.5</v>
       </c>
       <c r="G21">
-        <v>1116.5</v>
+        <v>1219.04</v>
       </c>
       <c r="H21">
-        <v>1219.04</v>
+        <v>1305.59</v>
       </c>
       <c r="I21">
-        <v>1305.59</v>
+        <v>1448.83</v>
       </c>
       <c r="J21">
-        <v>1448.83</v>
+        <v>1553.6</v>
       </c>
       <c r="K21">
-        <v>1553.6</v>
+        <v>1684.95</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4195,34 +4195,34 @@
         <v>84</v>
       </c>
       <c r="B22">
-        <v>32533.31</v>
+        <v>35700.74</v>
       </c>
       <c r="C22">
-        <v>35700.74</v>
+        <v>35417.16</v>
       </c>
       <c r="D22">
-        <v>35417.16</v>
+        <v>43804.72</v>
       </c>
       <c r="E22">
-        <v>43804.72</v>
+        <v>48861.7</v>
       </c>
       <c r="F22">
-        <v>48861.7</v>
+        <v>54344.09</v>
       </c>
       <c r="G22">
-        <v>54344.09</v>
+        <v>61457.96</v>
       </c>
       <c r="H22">
-        <v>61457.96</v>
+        <v>61934.09</v>
       </c>
       <c r="I22">
-        <v>61934.09</v>
+        <v>83686.61</v>
       </c>
       <c r="J22">
-        <v>83686.61</v>
+        <v>70410.93</v>
       </c>
       <c r="K22">
-        <v>70410.93</v>
+        <v>72786.55</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4230,34 +4230,34 @@
         <v>85</v>
       </c>
       <c r="B23">
-        <v>9750.12</v>
+        <v>10596.89</v>
       </c>
       <c r="C23">
-        <v>10596.89</v>
+        <v>12597.96</v>
       </c>
       <c r="D23">
-        <v>12597.96</v>
+        <v>12823.59</v>
       </c>
       <c r="E23">
-        <v>12823.59</v>
+        <v>13665.28</v>
       </c>
       <c r="F23">
-        <v>13665.28</v>
+        <v>14050.25</v>
       </c>
       <c r="G23">
-        <v>14050.25</v>
+        <v>15354.12</v>
       </c>
       <c r="H23">
-        <v>15354.12</v>
+        <v>17241.04</v>
       </c>
       <c r="I23">
-        <v>17241.04</v>
+        <v>18170.92</v>
       </c>
       <c r="J23">
-        <v>18170.92</v>
+        <v>21639.1</v>
       </c>
       <c r="K23">
-        <v>21639.1</v>
+        <v>24879.96</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4265,34 +4265,34 @@
         <v>86</v>
       </c>
       <c r="B24">
-        <v>66904.29</v>
+        <v>98497.5</v>
       </c>
       <c r="C24">
-        <v>98497.5</v>
+        <v>120077.51</v>
       </c>
       <c r="D24">
-        <v>120077.51</v>
+        <v>108417.44</v>
       </c>
       <c r="E24">
-        <v>108417.44</v>
+        <v>109260.45</v>
       </c>
       <c r="F24">
-        <v>109260.45</v>
+        <v>123309.85</v>
       </c>
       <c r="G24">
-        <v>123309.85</v>
+        <v>119317.73</v>
       </c>
       <c r="H24">
-        <v>119317.73</v>
+        <v>123822.44</v>
       </c>
       <c r="I24">
-        <v>123822.44</v>
+        <v>136443.32</v>
       </c>
       <c r="J24">
-        <v>136443.32</v>
+        <v>158439.58</v>
       </c>
       <c r="K24">
-        <v>158439.58</v>
+        <v>179429.56</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4300,34 +4300,34 @@
         <v>9</v>
       </c>
       <c r="B25">
-        <v>52828.39</v>
+        <v>68193.17</v>
       </c>
       <c r="C25">
-        <v>68193.17</v>
+        <v>77557.39</v>
       </c>
       <c r="D25">
-        <v>77557.39</v>
+        <v>77365.19</v>
       </c>
       <c r="E25">
-        <v>77365.19</v>
+        <v>98158.99</v>
       </c>
       <c r="F25">
-        <v>98158.99</v>
+        <v>107222.41</v>
       </c>
       <c r="G25">
-        <v>107222.41</v>
+        <v>117000.4</v>
       </c>
       <c r="H25">
-        <v>117000.4</v>
+        <v>122533.56</v>
       </c>
       <c r="I25">
-        <v>122533.56</v>
+        <v>155386.39</v>
       </c>
       <c r="J25">
-        <v>155386.39</v>
+        <v>173030.62</v>
       </c>
       <c r="K25">
-        <v>172405.53</v>
+        <v>197710.94</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4335,34 +4335,34 @@
         <v>10</v>
       </c>
       <c r="B26">
-        <v>2252.21</v>
+        <v>2914.68</v>
       </c>
       <c r="C26">
-        <v>2914.68</v>
+        <v>3105.07</v>
       </c>
       <c r="D26">
-        <v>3105.07</v>
+        <v>3495.89</v>
       </c>
       <c r="E26">
-        <v>3495.89</v>
+        <v>3661.56</v>
       </c>
       <c r="F26">
-        <v>3661.56</v>
+        <v>3711.06</v>
       </c>
       <c r="G26">
-        <v>3711.06</v>
+        <v>3691.27</v>
       </c>
       <c r="H26">
-        <v>3691.27</v>
+        <v>3695.6</v>
       </c>
       <c r="I26">
-        <v>3695.6</v>
+        <v>3849.12</v>
       </c>
       <c r="J26">
-        <v>3849.12</v>
+        <v>3991.48</v>
       </c>
       <c r="K26">
-        <v>3991.48</v>
+        <v>4829.72</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4370,34 +4370,34 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>143047.36</v>
+        <v>149114.67</v>
       </c>
       <c r="C27">
-        <v>149114.67</v>
+        <v>146602.98</v>
       </c>
       <c r="D27">
-        <v>146602.98</v>
+        <v>155867.46</v>
       </c>
       <c r="E27">
-        <v>155867.46</v>
+        <v>161123.8</v>
       </c>
       <c r="F27">
-        <v>161123.8</v>
+        <v>156010.17</v>
       </c>
       <c r="G27">
-        <v>156010.17</v>
+        <v>156194.34</v>
       </c>
       <c r="H27">
-        <v>156194.34</v>
+        <v>189980.82</v>
       </c>
       <c r="I27">
-        <v>189980.82</v>
+        <v>259736.05</v>
       </c>
       <c r="J27">
-        <v>259736.05</v>
+        <v>300943.34</v>
       </c>
       <c r="K27">
-        <v>300943.34</v>
+        <v>315004.81</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4405,34 +4405,34 @@
         <v>12</v>
       </c>
       <c r="B28">
-        <v>18176.79</v>
+        <v>944.83</v>
       </c>
       <c r="C28">
-        <v>944.83</v>
+        <v>-12244.91</v>
       </c>
       <c r="D28">
-        <v>-12244.91</v>
+        <v>5220.49</v>
       </c>
       <c r="E28">
-        <v>5220.49</v>
+        <v>30316.59</v>
       </c>
       <c r="F28">
-        <v>30316.59</v>
+        <v>32795.97</v>
       </c>
       <c r="G28">
-        <v>32795.97</v>
+        <v>49738.63</v>
       </c>
       <c r="H28">
-        <v>49738.63</v>
+        <v>75398.56</v>
       </c>
       <c r="I28">
-        <v>75398.56</v>
+        <v>91240.05</v>
       </c>
       <c r="J28">
-        <v>91240.05</v>
+        <v>106365.29</v>
       </c>
       <c r="K28">
-        <v>106365.29</v>
+        <v>114027.98</v>
       </c>
     </row>
     <row r="29" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4440,34 +4440,34 @@
         <v>13</v>
       </c>
       <c r="B29">
-        <v>5433.5</v>
+        <v>1335.5</v>
       </c>
       <c r="C29">
-        <v>1335.5</v>
+        <v>-8057.5</v>
       </c>
       <c r="D29">
-        <v>-8057.5</v>
+        <v>2151.41</v>
       </c>
       <c r="E29">
-        <v>2151.41</v>
+        <v>12139.76</v>
       </c>
       <c r="F29">
-        <v>12139.76</v>
+        <v>8516.25</v>
       </c>
       <c r="G29">
-        <v>8516.25</v>
+        <v>13382.46</v>
       </c>
       <c r="H29">
-        <v>13382.46</v>
+        <v>18840.13</v>
       </c>
       <c r="I29">
-        <v>18840.13</v>
+        <v>23101.79</v>
       </c>
       <c r="J29">
-        <v>23101.79</v>
+        <v>27348.14</v>
       </c>
       <c r="K29">
-        <v>27348.14</v>
+        <v>28859.51</v>
       </c>
     </row>
     <row r="30" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4475,34 +4475,34 @@
         <v>14</v>
       </c>
       <c r="B30">
-        <v>12224.6</v>
+        <v>241.23</v>
       </c>
       <c r="C30">
-        <v>241.23</v>
+        <v>-4556.29</v>
       </c>
       <c r="D30">
-        <v>-4556.29</v>
+        <v>2299.64</v>
       </c>
       <c r="E30">
-        <v>2299.64</v>
+        <v>19767.8</v>
       </c>
       <c r="F30">
-        <v>19767.8</v>
+        <v>22405.46</v>
       </c>
       <c r="G30">
-        <v>22405.46</v>
+        <v>35373.88</v>
       </c>
       <c r="H30">
-        <v>35373.88</v>
+        <v>55648.17</v>
       </c>
       <c r="I30">
-        <v>55648.17</v>
+        <v>67084.67</v>
       </c>
       <c r="J30">
-        <v>67084.67</v>
+        <v>77561.34</v>
       </c>
       <c r="K30">
-        <v>77561.34</v>
+        <v>83298.78</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4510,25 +4510,25 @@
         <v>70</v>
       </c>
       <c r="B31">
-        <v>2018.33</v>
-      </c>
-      <c r="C31">
         <v>2073.11</v>
       </c>
+      <c r="F31">
+        <v>3569.84</v>
+      </c>
       <c r="G31">
-        <v>3569.84</v>
+        <v>6336.47</v>
       </c>
       <c r="H31">
-        <v>6336.47</v>
+        <v>10084.8</v>
       </c>
       <c r="I31">
-        <v>10084.8</v>
+        <v>12226.7</v>
       </c>
       <c r="J31">
-        <v>12226.7</v>
+        <v>14190.11</v>
       </c>
       <c r="K31">
-        <v>14190.11</v>
+        <v>16015.09</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -4563,34 +4563,34 @@
         <v>38</v>
       </c>
       <c r="B41" s="16">
-        <v>45199.0</v>
+        <v>45382.0</v>
       </c>
       <c r="C41" s="16">
-        <v>45291.0</v>
+        <v>45473.0</v>
       </c>
       <c r="D41" s="16">
-        <v>45382.0</v>
+        <v>45565.0</v>
       </c>
       <c r="E41" s="16">
-        <v>45473.0</v>
+        <v>45657.0</v>
       </c>
       <c r="F41" s="16">
-        <v>45565.0</v>
+        <v>45747.0</v>
       </c>
       <c r="G41" s="16">
-        <v>45657.0</v>
+        <v>45838.0</v>
       </c>
       <c r="H41" s="16">
-        <v>45747.0</v>
+        <v>45930.0</v>
       </c>
       <c r="I41" s="16">
-        <v>45838.0</v>
+        <v>46022.0</v>
       </c>
       <c r="J41" s="16">
-        <v>45930.0</v>
+        <v>46112.0</v>
       </c>
       <c r="K41" s="16">
-        <v>46022.0</v>
+        <v>46203.0</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4598,34 +4598,34 @@
         <v>6</v>
       </c>
       <c r="B42">
-        <v>107390.78</v>
+        <v>117469.38</v>
       </c>
       <c r="C42">
-        <v>112868.34</v>
+        <v>118242.45</v>
       </c>
       <c r="D42">
-        <v>117469.38</v>
+        <v>121044.68</v>
       </c>
       <c r="E42">
-        <v>118242.45</v>
+        <v>124653.66</v>
       </c>
       <c r="F42">
-        <v>121044.68</v>
+        <v>126840.21</v>
       </c>
       <c r="G42">
-        <v>124653.66</v>
+        <v>125728.68</v>
       </c>
       <c r="H42">
-        <v>126997.0</v>
+        <v>128040.5</v>
       </c>
       <c r="I42">
-        <v>125728.68</v>
+        <v>130385.95</v>
       </c>
       <c r="J42">
-        <v>128040.5</v>
+        <v>131080.12</v>
       </c>
       <c r="K42">
-        <v>130589.72</v>
+        <v>136240.49</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4633,34 +4633,34 @@
         <v>7</v>
       </c>
       <c r="B43">
-        <v>59365.26</v>
+        <v>65418.48</v>
       </c>
       <c r="C43">
-        <v>62634.87</v>
+        <v>53996.5</v>
       </c>
       <c r="D43">
-        <v>65418.48</v>
+        <v>62709.31</v>
       </c>
       <c r="E43">
-        <v>53996.5</v>
+        <v>64890.43</v>
       </c>
       <c r="F43">
-        <v>62709.31</v>
+        <v>74438.45</v>
       </c>
       <c r="G43">
-        <v>64890.43</v>
+        <v>59496.24</v>
       </c>
       <c r="H43">
-        <v>74438.45</v>
+        <v>72265.35</v>
       </c>
       <c r="I43">
-        <v>59496.24</v>
+        <v>76799.07</v>
       </c>
       <c r="J43">
-        <v>72265.35</v>
+        <v>75050.08</v>
       </c>
       <c r="K43">
-        <v>76799.07</v>
+        <v>64930.49</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4668,34 +4668,34 @@
         <v>9</v>
       </c>
       <c r="B44">
-        <v>36865.34</v>
+        <v>47444.98</v>
       </c>
       <c r="C44">
-        <v>33103.3</v>
+        <v>33882.6</v>
       </c>
       <c r="D44">
-        <v>47444.98</v>
+        <v>42757.7</v>
       </c>
       <c r="E44">
-        <v>33882.6</v>
+        <v>43199.91</v>
       </c>
       <c r="F44">
-        <v>42757.7</v>
+        <v>52722.11</v>
       </c>
       <c r="G44">
-        <v>43199.91</v>
+        <v>41263.14</v>
       </c>
       <c r="H44">
-        <v>52565.32</v>
+        <v>50883.86</v>
       </c>
       <c r="I44">
-        <v>41263.14</v>
+        <v>55262.38</v>
       </c>
       <c r="J44">
-        <v>50883.86</v>
+        <v>49998.9</v>
       </c>
       <c r="K44">
-        <v>55058.61</v>
+        <v>43821.37</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4708,34 +4708,34 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>62955.15</v>
+        <v>70644.02</v>
       </c>
       <c r="C46">
-        <v>68091.94</v>
+        <v>71700.78</v>
       </c>
       <c r="D46">
-        <v>70644.02</v>
+        <v>73618.76</v>
       </c>
       <c r="E46">
-        <v>71700.78</v>
+        <v>77396.74</v>
       </c>
       <c r="F46">
-        <v>73618.76</v>
+        <v>78227.05</v>
       </c>
       <c r="G46">
-        <v>77396.74</v>
+        <v>78266.46</v>
       </c>
       <c r="H46">
-        <v>78227.05</v>
+        <v>78002.37</v>
       </c>
       <c r="I46">
-        <v>78266.46</v>
+        <v>78782.55</v>
       </c>
       <c r="J46">
-        <v>78002.37</v>
+        <v>79953.43</v>
       </c>
       <c r="K46">
-        <v>78782.55</v>
+        <v>82247.57</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4743,34 +4743,34 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>21935.71</v>
+        <v>28851.86</v>
       </c>
       <c r="C47">
-        <v>15244.83</v>
+        <v>26427.77</v>
       </c>
       <c r="D47">
-        <v>28851.86</v>
+        <v>27474.31</v>
       </c>
       <c r="E47">
-        <v>26427.77</v>
+        <v>25566.4</v>
       </c>
       <c r="F47">
-        <v>27474.31</v>
+        <v>26896.82</v>
       </c>
       <c r="G47">
-        <v>25566.4</v>
+        <v>29229.12</v>
       </c>
       <c r="H47">
-        <v>26896.82</v>
+        <v>28656.64</v>
       </c>
       <c r="I47">
-        <v>29229.12</v>
+        <v>30066.71</v>
       </c>
       <c r="J47">
-        <v>28656.64</v>
+        <v>26075.51</v>
       </c>
       <c r="K47">
-        <v>30066.71</v>
+        <v>32883.8</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4778,34 +4778,34 @@
         <v>13</v>
       </c>
       <c r="B48">
-        <v>5552.53</v>
+        <v>7115.39</v>
       </c>
       <c r="C48">
-        <v>3962.17</v>
+        <v>6746.97</v>
       </c>
       <c r="D48">
-        <v>7115.39</v>
+        <v>7254.69</v>
       </c>
       <c r="E48">
-        <v>6746.97</v>
+        <v>6391.05</v>
       </c>
       <c r="F48">
-        <v>7254.69</v>
+        <v>6955.43</v>
       </c>
       <c r="G48">
-        <v>6391.05</v>
+        <v>7602.48</v>
       </c>
       <c r="H48">
-        <v>6955.43</v>
+        <v>7152.15</v>
       </c>
       <c r="I48">
-        <v>7602.48</v>
+        <v>8190.67</v>
       </c>
       <c r="J48">
-        <v>7152.15</v>
+        <v>5914.21</v>
       </c>
       <c r="K48">
-        <v>8190.67</v>
+        <v>8304.76</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4813,34 +4813,34 @@
         <v>14</v>
       </c>
       <c r="B49">
-        <v>16099.58</v>
+        <v>21384.15</v>
       </c>
       <c r="C49">
-        <v>11064.14</v>
+        <v>19324.96</v>
       </c>
       <c r="D49">
-        <v>21384.15</v>
+        <v>19782.76</v>
       </c>
       <c r="E49">
-        <v>19324.96</v>
+        <v>18853.16</v>
       </c>
       <c r="F49">
-        <v>19782.76</v>
+        <v>19600.46</v>
       </c>
       <c r="G49">
-        <v>18853.16</v>
+        <v>21201.47</v>
       </c>
       <c r="H49">
-        <v>19600.46</v>
+        <v>21137.33</v>
       </c>
       <c r="I49">
-        <v>21201.47</v>
+        <v>21317.11</v>
       </c>
       <c r="J49">
-        <v>21137.33</v>
+        <v>19642.87</v>
       </c>
       <c r="K49">
-        <v>21317.11</v>
+        <v>24113.0</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -4848,34 +4848,34 @@
         <v>8</v>
       </c>
       <c r="B50">
-        <v>48025.52</v>
+        <v>52050.9</v>
       </c>
       <c r="C50">
-        <v>50233.47</v>
+        <v>64245.95</v>
       </c>
       <c r="D50">
-        <v>52050.9</v>
+        <v>58335.37</v>
       </c>
       <c r="E50">
-        <v>64245.95</v>
+        <v>59763.23</v>
       </c>
       <c r="F50">
-        <v>58335.37</v>
+        <v>52401.76</v>
       </c>
       <c r="G50">
-        <v>59763.23</v>
+        <v>66232.44</v>
       </c>
       <c r="H50">
-        <v>52558.55</v>
+        <v>55775.15</v>
       </c>
       <c r="I50">
-        <v>66232.44</v>
+        <v>53586.88</v>
       </c>
       <c r="J50">
-        <v>55775.15</v>
+        <v>56030.04</v>
       </c>
       <c r="K50">
-        <v>53790.65</v>
+        <v>71310.0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -4900,34 +4900,34 @@
         <v>38</v>
       </c>
       <c r="B56" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C56" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D56" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E56" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F56" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G56" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H56" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I56" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J56" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K56" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -4935,10 +4935,10 @@
         <v>24</v>
       </c>
       <c r="B57">
-        <v>776.28</v>
+        <v>797.35</v>
       </c>
       <c r="C57">
-        <v>797.35</v>
+        <v>892.46</v>
       </c>
       <c r="D57">
         <v>892.46</v>
@@ -4962,7 +4962,7 @@
         <v>892.46</v>
       </c>
       <c r="K57">
-        <v>892.46</v>
+        <v>923.06</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -4970,34 +4970,34 @@
         <v>25</v>
       </c>
       <c r="B58">
-        <v>179816.09</v>
+        <v>216394.8</v>
       </c>
       <c r="C58">
-        <v>216394.8</v>
+        <v>229429.49</v>
       </c>
       <c r="D58">
-        <v>229429.49</v>
+        <v>233603.2</v>
       </c>
       <c r="E58">
-        <v>233603.2</v>
+        <v>250167.66</v>
       </c>
       <c r="F58">
-        <v>250167.66</v>
+        <v>274669.1</v>
       </c>
       <c r="G58">
-        <v>274669.1</v>
+        <v>304695.58</v>
       </c>
       <c r="H58">
-        <v>304695.58</v>
+        <v>358038.86</v>
       </c>
       <c r="I58">
-        <v>358038.86</v>
+        <v>414046.71</v>
       </c>
       <c r="J58">
-        <v>414046.71</v>
+        <v>486144.3</v>
       </c>
       <c r="K58">
-        <v>486144.3</v>
+        <v>595207.81</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -5005,34 +5005,34 @@
         <v>71</v>
       </c>
       <c r="B59">
-        <v>2615256.95</v>
+        <v>2936176.32</v>
       </c>
       <c r="C59">
-        <v>2936176.32</v>
+        <v>3091257.62</v>
       </c>
       <c r="D59">
-        <v>3091257.62</v>
+        <v>3354288.72</v>
       </c>
       <c r="E59">
-        <v>3354288.72</v>
+        <v>3607061.3</v>
       </c>
       <c r="F59">
-        <v>3607061.3</v>
+        <v>4149127.45</v>
       </c>
       <c r="G59">
-        <v>4149127.45</v>
+        <v>4536570.38</v>
       </c>
       <c r="H59">
-        <v>4536570.38</v>
+        <v>4989687.46</v>
       </c>
       <c r="I59">
-        <v>4989687.46</v>
+        <v>5606146.99</v>
       </c>
       <c r="J59">
-        <v>5606146.99</v>
+        <v>6050755.27</v>
       </c>
       <c r="K59">
-        <v>6050755.27</v>
+        <v>6820399.27</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -5040,34 +5040,34 @@
         <v>72</v>
       </c>
       <c r="B60">
-        <v>276472.16</v>
+        <v>288391.04</v>
       </c>
       <c r="C60">
-        <v>288391.04</v>
+        <v>294859.6</v>
       </c>
       <c r="D60">
-        <v>294859.6</v>
+        <v>299675.65</v>
       </c>
       <c r="E60">
-        <v>299675.65</v>
+        <v>339364.31</v>
       </c>
       <c r="F60">
-        <v>339364.31</v>
+        <v>420925.83</v>
       </c>
       <c r="G60">
-        <v>420925.83</v>
+        <v>518719.42</v>
       </c>
       <c r="H60">
-        <v>518719.42</v>
+        <v>605795.73</v>
       </c>
       <c r="I60">
-        <v>605795.73</v>
+        <v>712669.43</v>
       </c>
       <c r="J60">
-        <v>712669.43</v>
+        <v>775937.87</v>
       </c>
       <c r="K60">
-        <v>775937.87</v>
+        <v>904645.84</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5075,34 +5075,34 @@
         <v>26</v>
       </c>
       <c r="B61">
-        <v>3072321.48</v>
+        <v>3441759.51</v>
       </c>
       <c r="C61">
-        <v>3441759.51</v>
+        <v>3616439.17</v>
       </c>
       <c r="D61">
-        <v>3616439.17</v>
+        <v>3888460.03</v>
       </c>
       <c r="E61">
-        <v>3888460.03</v>
+        <v>4197485.73</v>
       </c>
       <c r="F61">
-        <v>4197485.73</v>
+        <v>4845614.84</v>
       </c>
       <c r="G61">
-        <v>4845614.84</v>
+        <v>5360877.84</v>
       </c>
       <c r="H61">
-        <v>5360877.84</v>
+        <v>5954414.51</v>
       </c>
       <c r="I61">
-        <v>5954414.51</v>
+        <v>6733755.59</v>
       </c>
       <c r="J61">
-        <v>6733755.59</v>
+        <v>7313729.9</v>
       </c>
       <c r="K61">
-        <v>7313729.9</v>
+        <v>8321175.98</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -5110,34 +5110,34 @@
         <v>27</v>
       </c>
       <c r="B62">
-        <v>15415.21</v>
+        <v>51189.24</v>
       </c>
       <c r="C62">
-        <v>51189.24</v>
+        <v>42034.79</v>
       </c>
       <c r="D62">
-        <v>42034.79</v>
+        <v>39940.76</v>
       </c>
       <c r="E62">
-        <v>39940.76</v>
+        <v>39608.41</v>
       </c>
       <c r="F62">
-        <v>39608.41</v>
+        <v>41600.44</v>
       </c>
       <c r="G62">
-        <v>41600.44</v>
+        <v>41032.49</v>
       </c>
       <c r="H62">
-        <v>41032.49</v>
+        <v>45879.72</v>
       </c>
       <c r="I62">
-        <v>45879.72</v>
+        <v>46071.69</v>
       </c>
       <c r="J62">
-        <v>46071.69</v>
+        <v>47715.97</v>
       </c>
       <c r="K62">
-        <v>47715.97</v>
+        <v>59771.67</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -5145,34 +5145,34 @@
         <v>28</v>
       </c>
       <c r="B63">
-        <v>785.7</v>
+        <v>694.92</v>
       </c>
       <c r="C63">
-        <v>694.92</v>
+        <v>925.07</v>
       </c>
       <c r="D63">
-        <v>925.07</v>
+        <v>762.3</v>
       </c>
       <c r="E63">
-        <v>762.3</v>
+        <v>469.76</v>
       </c>
       <c r="F63">
-        <v>469.76</v>
+        <v>116.35</v>
       </c>
       <c r="G63">
-        <v>116.35</v>
+        <v>27.57</v>
       </c>
       <c r="H63">
-        <v>27.57</v>
+        <v>66.02</v>
       </c>
       <c r="I63">
-        <v>66.02</v>
+        <v>42.45</v>
       </c>
       <c r="J63">
-        <v>42.45</v>
+        <v>41.4</v>
       </c>
       <c r="K63">
-        <v>41.4</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -5180,34 +5180,34 @@
         <v>29</v>
       </c>
       <c r="B64">
-        <v>807374.58</v>
+        <v>1027280.87</v>
       </c>
       <c r="C64">
-        <v>1027280.87</v>
+        <v>1183794.24</v>
       </c>
       <c r="D64">
-        <v>1183794.24</v>
+        <v>1119269.82</v>
       </c>
       <c r="E64">
-        <v>1119269.82</v>
+        <v>1228284.28</v>
       </c>
       <c r="F64">
-        <v>1228284.28</v>
+        <v>1595100.27</v>
       </c>
       <c r="G64">
-        <v>1595100.27</v>
+        <v>1776489.9</v>
       </c>
       <c r="H64">
-        <v>1776489.9</v>
+        <v>1913107.86</v>
       </c>
       <c r="I64">
-        <v>1913107.86</v>
+        <v>2110548.23</v>
       </c>
       <c r="J64">
-        <v>2110548.23</v>
+        <v>2205601.11</v>
       </c>
       <c r="K64">
-        <v>2205601.11</v>
+        <v>2359502.17</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
@@ -5215,34 +5215,34 @@
         <v>73</v>
       </c>
       <c r="B65">
-        <v>2248745.99</v>
+        <v>2362594.48</v>
       </c>
       <c r="C65">
-        <v>2362594.48</v>
+        <v>2389685.07</v>
       </c>
       <c r="D65">
-        <v>2389685.07</v>
+        <v>2728487.15</v>
       </c>
       <c r="E65">
-        <v>2728487.15</v>
+        <v>2929123.28</v>
       </c>
       <c r="F65">
-        <v>2929123.28</v>
+        <v>3208797.78</v>
       </c>
       <c r="G65">
-        <v>3208797.78</v>
+        <v>3543327.88</v>
       </c>
       <c r="H65">
-        <v>3543327.88</v>
+        <v>3995360.91</v>
       </c>
       <c r="I65">
-        <v>3995360.91</v>
+        <v>4577093.22</v>
       </c>
       <c r="J65">
-        <v>4577093.22</v>
+        <v>5060371.42</v>
       </c>
       <c r="K65">
-        <v>5060371.42</v>
+        <v>5901824.28</v>
       </c>
     </row>
     <row r="66" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5250,34 +5250,34 @@
         <v>26</v>
       </c>
       <c r="B66">
-        <v>3072321.48</v>
+        <v>3441759.51</v>
       </c>
       <c r="C66">
-        <v>3441759.51</v>
+        <v>3616439.17</v>
       </c>
       <c r="D66">
-        <v>3616439.17</v>
+        <v>3888460.03</v>
       </c>
       <c r="E66">
-        <v>3888460.03</v>
+        <v>4197485.73</v>
       </c>
       <c r="F66">
-        <v>4197485.73</v>
+        <v>4845614.84</v>
       </c>
       <c r="G66">
-        <v>4845614.84</v>
+        <v>5360877.84</v>
       </c>
       <c r="H66">
-        <v>5360877.84</v>
+        <v>5954414.51</v>
       </c>
       <c r="I66">
-        <v>5954414.51</v>
+        <v>6733755.59</v>
       </c>
       <c r="J66">
-        <v>6733755.59</v>
+        <v>7313729.9</v>
       </c>
       <c r="K66">
-        <v>7313729.9</v>
+        <v>8321175.98</v>
       </c>
     </row>
     <row r="67" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5295,34 +5295,34 @@
         <v>87</v>
       </c>
       <c r="B69">
-        <v>142637.54</v>
+        <v>146076.35</v>
       </c>
       <c r="C69">
-        <v>146076.35</v>
+        <v>134973.43</v>
       </c>
       <c r="D69">
-        <v>134973.43</v>
+        <v>158218.46</v>
       </c>
       <c r="E69">
-        <v>158218.46</v>
+        <v>146633.51</v>
       </c>
       <c r="F69">
-        <v>146633.51</v>
+        <v>189807.29</v>
       </c>
       <c r="G69">
-        <v>189807.29</v>
+        <v>296525.21</v>
       </c>
       <c r="H69">
-        <v>296525.21</v>
+        <v>225692.63</v>
       </c>
       <c r="I69">
-        <v>225692.63</v>
+        <v>206766.69</v>
       </c>
       <c r="J69">
-        <v>206766.69</v>
+        <v>208893.69</v>
       </c>
       <c r="K69">
-        <v>208893.69</v>
+        <v>247107.52</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
@@ -5330,13 +5330,13 @@
         <v>74</v>
       </c>
       <c r="B70">
-        <v>7762777042.0</v>
+        <v>7973504442.0</v>
       </c>
       <c r="C70">
-        <v>7973504442.0</v>
+        <v>8924587534.0</v>
       </c>
       <c r="D70">
-        <v>8924587534.0</v>
+        <v>8924611534.0</v>
       </c>
       <c r="E70">
         <v>8924611534.0</v>
@@ -5348,16 +5348,16 @@
         <v>8924611534.0</v>
       </c>
       <c r="H70">
-        <v>8924611534.0</v>
+        <v>8924611934.0</v>
       </c>
       <c r="I70">
         <v>8924611934.0</v>
       </c>
       <c r="J70">
-        <v>8924611934.0</v>
+        <v>8924620034.0</v>
       </c>
       <c r="K70">
-        <v>8924620034.0</v>
+        <v>9230617586.0</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
@@ -5428,34 +5428,34 @@
         <v>38</v>
       </c>
       <c r="B81" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C81" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D81" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E81" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F81" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G81" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H81" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I81" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J81" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K81" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5463,34 +5463,34 @@
         <v>32</v>
       </c>
       <c r="B82">
-        <v>14476.68</v>
+        <v>77406.0</v>
       </c>
       <c r="C82">
-        <v>77406.0</v>
+        <v>-96507.91</v>
       </c>
       <c r="D82">
-        <v>-96507.91</v>
+        <v>29556.01</v>
       </c>
       <c r="E82">
-        <v>29556.01</v>
+        <v>23928.53</v>
       </c>
       <c r="F82">
-        <v>23928.53</v>
+        <v>89918.93</v>
       </c>
       <c r="G82">
-        <v>89918.93</v>
+        <v>57694.85</v>
       </c>
       <c r="H82">
-        <v>57694.85</v>
+        <v>-86013.68</v>
       </c>
       <c r="I82">
-        <v>-86013.68</v>
+        <v>21632.43</v>
       </c>
       <c r="J82">
-        <v>21632.43</v>
+        <v>45484.01</v>
       </c>
       <c r="K82">
-        <v>48486.29</v>
+        <v>38097.39</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5498,34 +5498,34 @@
         <v>33</v>
       </c>
       <c r="B83">
-        <v>-2746.71</v>
+        <v>-4571.83</v>
       </c>
       <c r="C83">
-        <v>-4571.83</v>
+        <v>13052.7</v>
       </c>
       <c r="D83">
-        <v>13052.7</v>
+        <v>219.51</v>
       </c>
       <c r="E83">
-        <v>219.51</v>
+        <v>-555.05</v>
       </c>
       <c r="F83">
-        <v>-555.05</v>
+        <v>-3669.83</v>
       </c>
       <c r="G83">
-        <v>-3669.83</v>
+        <v>-2652.25</v>
       </c>
       <c r="H83">
-        <v>-2652.25</v>
+        <v>-965.91</v>
       </c>
       <c r="I83">
-        <v>-965.91</v>
+        <v>-3475.76</v>
       </c>
       <c r="J83">
-        <v>-3475.76</v>
+        <v>-3386.58</v>
       </c>
       <c r="K83">
-        <v>-3386.58</v>
+        <v>9240.01</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5533,34 +5533,34 @@
         <v>34</v>
       </c>
       <c r="B84">
-        <v>4348.45</v>
+        <v>-4196.48</v>
       </c>
       <c r="C84">
-        <v>-4196.48</v>
+        <v>5547.16</v>
       </c>
       <c r="D84">
-        <v>5547.16</v>
+        <v>447.64</v>
       </c>
       <c r="E84">
-        <v>447.64</v>
+        <v>5429.52</v>
       </c>
       <c r="F84">
-        <v>5429.52</v>
+        <v>7142.67</v>
       </c>
       <c r="G84">
-        <v>7142.67</v>
+        <v>-3844.51</v>
       </c>
       <c r="H84">
-        <v>-3844.51</v>
+        <v>6386.38</v>
       </c>
       <c r="I84">
-        <v>6386.38</v>
+        <v>-9896.28</v>
       </c>
       <c r="J84">
-        <v>-9896.28</v>
+        <v>-10736.79</v>
       </c>
       <c r="K84">
-        <v>-13739.08</v>
+        <v>-3427.14</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5568,34 +5568,34 @@
         <v>35</v>
       </c>
       <c r="B85">
-        <v>16078.42</v>
+        <v>68637.69</v>
       </c>
       <c r="C85">
-        <v>68637.69</v>
+        <v>-77908.05</v>
       </c>
       <c r="D85">
-        <v>-77908.05</v>
+        <v>30223.16</v>
       </c>
       <c r="E85">
-        <v>30223.16</v>
+        <v>28803.0</v>
       </c>
       <c r="F85">
-        <v>28803.0</v>
+        <v>93391.77</v>
       </c>
       <c r="G85">
-        <v>93391.77</v>
+        <v>51198.09</v>
       </c>
       <c r="H85">
-        <v>51198.09</v>
+        <v>-80593.21</v>
       </c>
       <c r="I85">
-        <v>-80593.21</v>
+        <v>8260.39</v>
       </c>
       <c r="J85">
-        <v>8260.39</v>
+        <v>31360.64</v>
       </c>
       <c r="K85">
-        <v>31360.64</v>
+        <v>43910.27</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -5615,34 +5615,34 @@
         <v>77</v>
       </c>
       <c r="B90">
-        <v>194.25</v>
+        <v>293.4</v>
       </c>
       <c r="C90">
-        <v>293.4</v>
+        <v>249.9</v>
       </c>
       <c r="D90">
-        <v>249.9</v>
+        <v>320.75</v>
       </c>
       <c r="E90">
-        <v>320.75</v>
+        <v>196.85</v>
       </c>
       <c r="F90">
-        <v>196.85</v>
+        <v>364.3</v>
       </c>
       <c r="G90">
-        <v>364.3</v>
+        <v>493.55</v>
       </c>
       <c r="H90">
-        <v>493.55</v>
+        <v>523.75</v>
       </c>
       <c r="I90">
-        <v>523.75</v>
+        <v>752.35</v>
       </c>
       <c r="J90">
-        <v>752.35</v>
+        <v>771.5</v>
       </c>
       <c r="K90">
-        <v>771.5</v>
+        <v>979.4</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5655,10 +5655,10 @@
         <v>89</v>
       </c>
       <c r="B93" s="31">
-        <v>776.28</v>
+        <v>797.35</v>
       </c>
       <c r="C93" s="31">
-        <v>797.35</v>
+        <v>892.46</v>
       </c>
       <c r="D93" s="31">
         <v>892.46</v>
@@ -5682,7 +5682,7 @@
         <v>892.46</v>
       </c>
       <c r="K93" s="31">
-        <v>892.46</v>
+        <v>923.06</v>
       </c>
     </row>
   </sheetData>
